--- a/naver-place-crawler/results_derma/영도구_피부과.xlsx
+++ b/naver-place-crawler/results_derma/영도구_피부과.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>제이린의원 남포점</t>
+          <t>맑은피부과의원</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bekusama@naver.com</t>
+          <t>8332175@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1305-7601</t>
+          <t>051-243-7700</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 중구 구덕로 5 10, 11층</t>
+          <t>부산광역시 서구 보수대로 9 2층 201호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://nampo.jryn.co.kr/</t>
+          <t>http://www.thepureskin.co.kr/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -612,22 +612,22 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1487</v>
+        <v>505</v>
       </c>
       <c r="Q2" t="n">
-        <v>456</v>
+        <v>2128</v>
       </c>
       <c r="R2" t="n">
-        <v>1943</v>
+        <v>2633</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1852887352</t>
+          <t>37615167</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1852887352</t>
+          <t>https://m.place.naver.com/place/37615167</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -658,44 +658,44 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>디데이의원 부산</t>
+          <t>제이린의원 남포점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ddaymnp0001@naver.com</t>
+          <t>bekusama@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>051-245-3210</t>
+          <t>0507-1305-7601</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 중구 구덕로34번길 4 뉴 남포빌딩 2층</t>
+          <t>부산광역시 중구 구덕로 5 10, 11층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://dday.clinic</t>
+          <t>https://nampo.jryn.co.kr/event_view.php</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1201</v>
+        <v>1489</v>
       </c>
       <c r="Q3" t="n">
-        <v>3588</v>
+        <v>463</v>
       </c>
       <c r="R3" t="n">
-        <v>4789</v>
+        <v>1952</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1508654704</t>
+          <t>1852887352</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1508654704</t>
+          <t>https://m.place.naver.com/place/1852887352</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -752,24 +752,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>미드림피부과의원</t>
+          <t>설피부과의원</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nidunadu@naver.com</t>
+          <t>purebabyface1@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>051-412-2375</t>
+          <t>051-463-3831</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 97 5층 미드림피부과의원</t>
+          <t>부산광역시 중구 대청로 81</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>742</v>
+        <v>410</v>
       </c>
       <c r="Q4" t="n">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>827</v>
+        <v>414</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,56 +824,52 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>37675639</t>
+          <t>19532976</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37675639</t>
+          <t>https://m.place.naver.com/place/19532976</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>피부과</t>
+          <t>공중전화</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>고운피부과의원</t>
+          <t>설피부과앞_옥외</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lamisi@naver.com</t>
+          <t>dearlytoheart@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>051-231-4001</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 중구 구덕로 40 호림빌딩 4층</t>
+          <t>부산광역시 중구 대청로 79</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://gounnpo.com/template/main/main.php</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -899,17 +895,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>685</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1635</v>
+        <v>0</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +914,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>13249383</t>
+          <t>1631766608</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13249383</t>
+          <t>https://m.place.naver.com/place/1631766608</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -940,29 +936,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>더맑은의원</t>
+          <t>미소안의원</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>178cm74kg@naver.com</t>
+          <t>prescribe6145@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>051-404-1221</t>
+          <t>051-257-0097</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼로 12 1층</t>
+          <t>부산광역시 중구 구덕로 40 12층 미소안의원</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.misoan.kr/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,7 +968,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -993,17 +989,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>216</v>
+        <v>609</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>303</v>
       </c>
       <c r="R6" t="n">
-        <v>220</v>
+        <v>912</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1008,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>337048381</t>
+          <t>1369690026</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/337048381</t>
+          <t>https://m.place.naver.com/place/1369690026</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1030,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>블리비의원 부산남포점</t>
+          <t>더맑은의원</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lovewriting2023@naver.com</t>
+          <t>178cm74kg@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1811-6686</t>
+          <t>051-404-1221</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 중구 구덕로 40 2층(남포동2가, 호림빌딩)</t>
+          <t>부산광역시 영도구 동삼로 12 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://www.velyb.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1066,7 +1062,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1091,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2674</v>
+        <v>217</v>
       </c>
       <c r="Q7" t="n">
-        <v>4810</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>7484</v>
+        <v>221</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1068082939</t>
+          <t>337048381</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1068082939</t>
+          <t>https://m.place.naver.com/place/337048381</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1128,24 +1124,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>설피부과의원</t>
+          <t>미드림피부과의원</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>purebabyface1@naver.com</t>
+          <t>nidunadu@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>051-463-3831</t>
+          <t>051-412-2375</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 중구 대청로 81</t>
+          <t>부산광역시 영도구 태종로 97 5층 미드림피부과의원</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1185,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>410</v>
+        <v>741</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="R8" t="n">
-        <v>413</v>
+        <v>826</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>19532976</t>
+          <t>37675639</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19532976</t>
+          <t>https://m.place.naver.com/place/37675639</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1221,11 @@
           <t>고운피부과의원</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>cjswn2276@naver.com</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>khahn@interactivy.com</t>
@@ -1282,10 +1282,10 @@
         <v>508</v>
       </c>
       <c r="Q9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R9" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1316,34 +1316,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>맑은피부과의원</t>
+          <t>디데이의원 부산</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dongtanskin@naver.com</t>
+          <t>ddaymnp0001@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>051-243-7700</t>
+          <t>051-245-3210</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 서구 보수대로 9 2층 201호</t>
+          <t>부산광역시 중구 구덕로34번길 4 뉴 남포빌딩 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://www.thepureskin.co.kr/</t>
+          <t>https://dday.clinic</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1369,17 +1369,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>504</v>
+        <v>1217</v>
       </c>
       <c r="Q10" t="n">
-        <v>2136</v>
+        <v>3040</v>
       </c>
       <c r="R10" t="n">
-        <v>2640</v>
+        <v>4257</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1388,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>37615167</t>
+          <t>1508654704</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37615167</t>
+          <t>https://m.place.naver.com/place/1508654704</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1410,39 +1410,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>새로고침의원</t>
+          <t>가온미의원</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>effect5377@naver.com</t>
+          <t>supervisor0128@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1325-7988</t>
+          <t>051-244-0128</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 중구 광복로 73 2층</t>
+          <t>부산광역시 중구 흑교로 6 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://lamarclinic.co.kr</t>
+          <t>https://blog.naver.com/supervisor0128</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1458,22 +1458,22 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="Q11" t="n">
-        <v>388</v>
+        <v>22</v>
       </c>
       <c r="R11" t="n">
-        <v>516</v>
+        <v>111</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,43 +1482,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1454273873</t>
+          <t>35673052</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1454273873</t>
+          <t>https://m.place.naver.com/place/35673052</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>공중전화</t>
+          <t>피부과</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>설피부과앞_옥외</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>블리비의원 부산남포점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>jin30811@naver.com</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1811-6686</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산광역시 중구 대청로 79</t>
+          <t>부산광역시 중구 구덕로 40 2층(남포동2가, 호림빌딩)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.velyb.kr</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1528,7 +1536,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1553,13 +1561,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2726</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4587</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>7313</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,17 +1576,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1631766608</t>
+          <t>1068082939</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1631766608</t>
+          <t>https://m.place.naver.com/place/1068082939</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1590,39 +1598,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>미소안의원</t>
+          <t>고운피부과의원</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>prescribe6145@naver.com</t>
+          <t>lamisi@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>051-257-0097</t>
+          <t>051-231-4001</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>부산광역시 중구 구덕로 40 12층 미소안의원</t>
+          <t>부산광역시 중구 구덕로 40 호림빌딩 4층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.misoan.kr/</t>
+          <t>http://gounnpo.com/template/main/main.php</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1647,13 +1655,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>599</v>
+        <v>951</v>
       </c>
       <c r="Q13" t="n">
-        <v>298</v>
+        <v>688</v>
       </c>
       <c r="R13" t="n">
-        <v>897</v>
+        <v>1639</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,17 +1670,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1369690026</t>
+          <t>13249383</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1369690026</t>
+          <t>https://m.place.naver.com/place/13249383</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1684,39 +1692,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>가온미의원</t>
+          <t>새로고침의원</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>supervisor0128@naver.com</t>
+          <t>effect5377@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>051-244-0128</t>
+          <t>0507-1325-7988</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>부산광역시 중구 흑교로 6 3층</t>
+          <t>부산광역시 중구 광복로 73 2층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/supervisor0128</t>
+          <t>https://lamarclinic.co.kr</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1732,22 +1740,22 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="Q14" t="n">
-        <v>22</v>
+        <v>390</v>
       </c>
       <c r="R14" t="n">
-        <v>111</v>
+        <v>518</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,17 +1764,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>35673052</t>
+          <t>1454273873</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35673052</t>
+          <t>https://m.place.naver.com/place/1454273873</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1789,11 @@
           <t>참조은의원</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>designmare20@naver.com</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
@@ -1856,7 +1868,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1928,10 +1940,10 @@
         <v>9</v>
       </c>
       <c r="Q16" t="n">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="R16" t="n">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1950,7 +1962,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1962,29 +1974,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>연세의원</t>
+          <t>몸사랑내과의원</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>goodbalance22@naver.com</t>
+          <t>samsebody@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>051-405-7797</t>
+          <t>051-413-0055</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 와치로 250 3층</t>
+          <t>부산광역시 영도구 절영로 30 삼세메디칼6층601호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://momsarang.or.kr/</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1994,12 +2006,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2015,17 +2027,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>121</v>
+        <v>807</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="R17" t="n">
-        <v>125</v>
+        <v>818</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2034,17 +2046,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>20380812</t>
+          <t>38411752</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20380812</t>
+          <t>https://m.place.naver.com/place/38411752</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2056,24 +2068,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>장편한내과의원</t>
+          <t>형건덕내과의원</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>asanjang0062@naver.com</t>
+          <t>lsuk0070@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>051-404-1088</t>
+          <t>0507-1406-2023</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼로 12</t>
+          <t>부산광역시 영도구 대교로 1 미라클타워 4층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2113,13 +2125,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>836</v>
+        <v>205</v>
       </c>
       <c r="Q18" t="n">
         <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>839</v>
+        <v>208</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2128,17 +2140,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>13250072</t>
+          <t>1138505292</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13250072</t>
+          <t>https://m.place.naver.com/place/1138505292</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2150,44 +2162,48 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>형건덕내과의원</t>
+          <t>일신내과의원</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>lsuk0070@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>guard191@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>kyb216@gmail.com</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1406-2023</t>
+          <t>0507-1351-9846</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 대교로 1 미라클타워 4층</t>
+          <t>부산광역시 영도구 수정길 191 일신내과의원</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://ilshinintclinic-mo.imweb.me</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2203,17 +2219,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>205</v>
+        <v>690</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>208</v>
+        <v>691</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2222,17 +2238,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1138505292</t>
+          <t>13250186</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138505292</t>
+          <t>https://m.place.naver.com/place/13250186</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2244,24 +2260,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>더조은의원</t>
+          <t>한가족내과신경외과의원</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>rjsdud86@naver.com</t>
+          <t>daewha2014@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>051-405-5758</t>
+          <t>051-405-6546</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 상리로 25</t>
+          <t>부산광역시 영도구 와치로 252</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2301,13 +2317,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>272</v>
+        <v>374</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>272</v>
+        <v>375</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2316,17 +2332,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>36604640</t>
+          <t>16389204</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36604640</t>
+          <t>https://m.place.naver.com/place/16389204</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2338,24 +2354,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>한가족내과신경외과의원</t>
+          <t>건강한내과의원</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>kcmkcm0071@naver.com</t>
+          <t>healthyman2021@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>051-405-6546</t>
+          <t>051-403-2333</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 와치로 252</t>
+          <t>부산광역시 영도구 동삼로 64 농협중앙회 4층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2395,13 +2411,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>374</v>
+        <v>280</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>375</v>
+        <v>282</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2410,17 +2426,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>16389204</t>
+          <t>33252510</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16389204</t>
+          <t>https://m.place.naver.com/place/33252510</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2432,24 +2448,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>건강한내과의원</t>
+          <t>한마음의원</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>healthyman2021@naver.com</t>
+          <t>sodium9654@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>051-403-2333</t>
+          <t>051-416-9095</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼로 64 농협중앙회 4층</t>
+          <t>부산광역시 영도구 태종로 332</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2489,13 +2505,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>280</v>
+        <v>102</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>282</v>
+        <v>102</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2504,17 +2520,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>33252510</t>
+          <t>32064889</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33252510</t>
+          <t>https://m.place.naver.com/place/32064889</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2526,24 +2542,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>강남의원</t>
+          <t>한빛연합의원</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>medi114_official@naver.com</t>
+          <t>kimeun57@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>051-416-4015</t>
+          <t>051-405-8633</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 꿈나무길 183 강남병원</t>
+          <t>부산광역시 영도구 상리로 33</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2583,13 +2599,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>48</v>
+        <v>163</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>51</v>
+        <v>163</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2598,17 +2614,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>13250154</t>
+          <t>21543850</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13250154</t>
+          <t>https://m.place.naver.com/place/21543850</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2620,24 +2636,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>흰여울의원</t>
+          <t>장편한내과의원</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>clftns0305@naver.com</t>
+          <t>asanjang0062@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>051-417-5777</t>
+          <t>051-404-1088</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 하나길 608 1층</t>
+          <t>부산광역시 영도구 동삼로 12</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2677,13 +2693,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>838</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>841</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2692,17 +2708,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2082170896</t>
+          <t>13250072</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2082170896</t>
+          <t>https://m.place.naver.com/place/13250072</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2714,24 +2730,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>수도의원</t>
+          <t>더조은의원</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>wisedr-agt@naver.com</t>
+          <t>rjsdud86@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>051-416-4031</t>
+          <t>051-405-5758</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 봉래동4가 116-3</t>
+          <t>부산광역시 영도구 상리로 25</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2771,13 +2787,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>398</v>
+        <v>272</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>399</v>
+        <v>272</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2786,17 +2802,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>13250155</t>
+          <t>36604640</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13250155</t>
+          <t>https://m.place.naver.com/place/36604640</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2808,24 +2824,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>한빛연합의원</t>
+          <t>강남의원</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>kimeun57@naver.com</t>
+          <t>medi114_official@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>051-405-8633</t>
+          <t>051-416-4015</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 상리로 33</t>
+          <t>부산광역시 영도구 꿈나무길 183 강남병원</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2865,13 +2881,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>163</v>
+        <v>48</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>163</v>
+        <v>51</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2880,17 +2896,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>21543850</t>
+          <t>13250154</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21543850</t>
+          <t>https://m.place.naver.com/place/13250154</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2902,29 +2918,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>몸사랑내과의원</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>samsebody@naver.com</t>
-        </is>
-      </c>
+          <t>수도의원</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>051-413-0055</t>
+          <t>051-416-4031</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 절영로 30 삼세메디칼6층601호</t>
+          <t>부산광역시 영도구 봉래동4가 116-3</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>http://momsarang.or.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2934,12 +2946,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2955,17 +2967,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>793</v>
+        <v>398</v>
       </c>
       <c r="Q27" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>804</v>
+        <v>399</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2974,17 +2986,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>38411752</t>
+          <t>13250155</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38411752</t>
+          <t>https://m.place.naver.com/place/13250155</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2996,44 +3008,40 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>일신내과의원</t>
+          <t>연세의원</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>kyb216@gmail.com</t>
-        </is>
-      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1351-9846</t>
+          <t>051-405-7797</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 수정길 191 일신내과의원</t>
+          <t>부산광역시 영도구 와치로 250 3층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://ilshinintclinic-mo.imweb.me</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3049,17 +3057,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>690</v>
+        <v>121</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R28" t="n">
-        <v>691</v>
+        <v>126</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3068,46 +3076,46 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>13250186</t>
+          <t>20380812</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13250186</t>
+          <t>https://m.place.naver.com/place/20380812</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>내과</t>
+          <t>병원,의원</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>한마음의원</t>
+          <t>서울시원의원</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>sodium9654@naver.com</t>
+          <t>siwonpain2020@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>051-416-9095</t>
+          <t>051-412-0110</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 332</t>
+          <t>부산광역시 영도구 남항로 7</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3147,13 +3155,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3162,17 +3170,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>32064889</t>
+          <t>1557492903</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32064889</t>
+          <t>https://m.place.naver.com/place/1557492903</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3184,24 +3192,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>서울시원의원</t>
+          <t>푸른의원</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>siwonpain2020@naver.com</t>
+          <t>prnh5028@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>051-412-0110</t>
+          <t>051-417-1114</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 남항로 7</t>
+          <t>부산광역시 영도구 하나길 693 2층,3층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3241,13 +3249,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1</v>
+        <v>142</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>142</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3256,17 +3264,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1557492903</t>
+          <t>19867109</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1557492903</t>
+          <t>https://m.place.naver.com/place/19867109</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3289,11 @@
           <t>고려의원</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1560kor2@naver.com</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
@@ -3356,32 +3368,36 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>병원,의원</t>
+          <t>비뇨의학과</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>푸른의원</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>성비뇨기과의원</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>binterest@naver.com</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>051-417-1114</t>
+          <t>051-245-7272</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 하나길 693 2층,3층</t>
+          <t>부산광역시 서구 구덕로 109 10층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3421,13 +3437,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>142</v>
+        <v>32</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>142</v>
+        <v>33</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3436,17 +3452,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>19867109</t>
+          <t>108949197</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19867109</t>
+          <t>https://m.place.naver.com/place/108949197</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3458,20 +3474,24 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>성비뇨기과의원</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>강남고운의원</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>thegounclinic@naver.com</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>051-245-7272</t>
+          <t>051-416-8009</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>부산광역시 서구 구덕로 109 10층</t>
+          <t>부산광역시 영도구 태종로 93 7층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3511,13 +3531,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>32</v>
+        <v>392</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>33</v>
+        <v>395</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3526,62 +3546,66 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>108949197</t>
+          <t>10971924</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/108949197</t>
+          <t>https://m.place.naver.com/place/10971924</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>비뇨의학과</t>
+          <t>성형외과</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>강남고운의원</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>센스원의원</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>kka_mii@naver.com</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>051-416-8009</t>
+          <t>051-245-2893</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 93 7층</t>
+          <t>부산광역시 중구 보수대로 18 2층 센스원의원</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://senseoneps.com/</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3601,13 +3625,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>392</v>
+        <v>34</v>
       </c>
       <c r="Q34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>394</v>
+        <v>35</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3616,66 +3640,66 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>10971924</t>
+          <t>37944826</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/10971924</t>
+          <t>https://m.place.naver.com/place/37944826</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>성형외과</t>
+          <t>소아청소년과</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>센스원의원</t>
+          <t>최덕철소아청소년과의원</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>kka_mii@naver.com</t>
+          <t>asdasdqsss@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>051-245-2893</t>
+          <t>051-405-8833</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>부산광역시 중구 보수대로 18 2층 센스원의원</t>
+          <t>부산광역시 영도구 동삼로 23</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>http://senseoneps.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3695,13 +3719,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R35" t="n">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3710,17 +3734,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>37944826</t>
+          <t>13250093</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37944826</t>
+          <t>https://m.place.naver.com/place/13250093</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3789,13 +3813,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="Q36" t="n">
         <v>30</v>
       </c>
       <c r="R36" t="n">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3814,41 +3838,41 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>소아청소년과</t>
+          <t>요양병원</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>최덕철소아청소년과의원</t>
+          <t>영도참편한요양병원</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>asdasdqsss@naver.com</t>
+          <t>ydchampyonhan@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>051-405-8833</t>
+          <t>051-403-9971</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼로 23</t>
+          <t>부산광역시 영도구 동삼서로 21 영도참편한요양병원</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.ydchampyonhan.com/ko/</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3858,7 +3882,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3879,17 +3903,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="Q37" t="n">
-        <v>6</v>
+        <v>99</v>
       </c>
       <c r="R37" t="n">
-        <v>71</v>
+        <v>182</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3898,17 +3922,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>13250093</t>
+          <t>30824156</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13250093</t>
+          <t>https://m.place.naver.com/place/30824156</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3920,29 +3944,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>영도참편한요양병원</t>
+          <t>정요양병원</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ydchampyonhan@naver.com</t>
+          <t>jeoung-hp@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>051-403-9971</t>
+          <t>1899-0071</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼서로 21 영도참편한요양병원</t>
+          <t>부산광역시 영도구 절영로 32</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.ydchampyonhan.com/ko/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3952,7 +3976,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3973,17 +3997,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="Q38" t="n">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="R38" t="n">
-        <v>179</v>
+        <v>84</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3992,61 +4016,61 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>30824156</t>
+          <t>31705007</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/30824156</t>
+          <t>https://m.place.naver.com/place/31705007</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>요양병원</t>
+          <t>의료용품,기기제조</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>정요양병원</t>
+          <t>수도그룹</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jeoung-hp@naver.com</t>
+          <t>whitegirl30@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1899-0071</t>
+          <t>051-416-1560</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 절영로 32</t>
+          <t>부산광역시 영도구 봉래동4가 116-3 수도빌딩 7층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.soodogroup.com/</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4071,13 +4095,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>83</v>
+        <v>5</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4086,56 +4110,56 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>31705007</t>
+          <t>32323636</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31705007</t>
+          <t>https://m.place.naver.com/place/32323636</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>의료용품,기기제조</t>
+          <t>이비인후과</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>수도그룹</t>
+          <t>오션이비인후과의원</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>whitegirl30@naver.com</t>
+          <t>ydentocean@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>051-416-1560</t>
+          <t>0507-1409-1007</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 봉래동4가 116-3 수도빌딩 7층</t>
+          <t>부산광역시 영도구 동삼로 56 한나타워 2층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://www.soodogroup.com/</t>
+          <t>https://blog.naver.com/ydentocean</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4145,7 +4169,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4165,13 +4189,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3</v>
+        <v>540</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="R40" t="n">
-        <v>5</v>
+        <v>560</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4180,17 +4204,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>32323636</t>
+          <t>1796239016</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32323636</t>
+          <t>https://m.place.naver.com/place/1796239016</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4202,29 +4226,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>오션이비인후과의원</t>
+          <t>이지숨이비인후과의원</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ydentocean@naver.com</t>
+          <t>ssmedi1001@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1409-1007</t>
+          <t>0507-1424-0130</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼로 56 한나타워 2층</t>
+          <t>부산광역시 중구 구덕로 40 호림빌딩 7층</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ydentocean</t>
+          <t>https://blog.naver.com/ssmedi1001</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4259,13 +4283,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="Q41" t="n">
-        <v>19</v>
+        <v>3010</v>
       </c>
       <c r="R41" t="n">
-        <v>558</v>
+        <v>3556</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4274,61 +4298,61 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1796239016</t>
+          <t>20601821</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1796239016</t>
+          <t>https://m.place.naver.com/place/20601821</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>이비인후과</t>
+          <t>재활의학과</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>이지숨이비인후과의원</t>
+          <t>몸편한 제통 재활의학과의원</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ssmedi1001@naver.com</t>
+          <t>bodyrelaxrehab@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1424-0130</t>
+          <t>051-715-2525</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>부산광역시 중구 구덕로 40 호림빌딩 7층</t>
+          <t>부산광역시 영도구 동삼로 12 3층, 4층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ssmedi1001</t>
+          <t>http://www.bodyrelaxrm.com/</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4344,7 +4368,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4353,13 +4377,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>546</v>
+        <v>794</v>
       </c>
       <c r="Q42" t="n">
-        <v>2998</v>
+        <v>222</v>
       </c>
       <c r="R42" t="n">
-        <v>3544</v>
+        <v>1016</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4368,56 +4392,52 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>20601821</t>
+          <t>1013979454</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20601821</t>
+          <t>https://m.place.naver.com/place/1013979454</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>재활의학과</t>
+          <t>정신건강의학과</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>몸편한 제통 재활의학과의원</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>bodyrelaxrehab@naver.com</t>
-        </is>
-      </c>
+          <t>e맑은정신과의원</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>051-715-2525</t>
+          <t>051-415-5307</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼로 12 3층, 4층</t>
+          <t>부산광역시 영도구 태종로 97 영도메디칼빌딩</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>http://www.bodyrelaxrm.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4427,7 +4447,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4438,7 +4458,7 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4447,13 +4467,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>792</v>
+        <v>92</v>
       </c>
       <c r="Q43" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1010</v>
+        <v>92</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4462,56 +4482,56 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1013979454</t>
+          <t>13250140</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1013979454</t>
+          <t>https://m.place.naver.com/place/13250140</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>정신건강의학과</t>
+          <t>정형외과</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>e맑은정신과의원</t>
+          <t>건강만세365병원</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>guard191@naver.com</t>
+          <t>manse365hp@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>051-415-5307</t>
+          <t>051-711-0365</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 97 영도메디칼빌딩</t>
+          <t>부산광역시 중구 대청로 105</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.manse365.com/</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4521,7 +4541,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4532,22 +4552,22 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>92</v>
+        <v>322</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="R44" t="n">
-        <v>92</v>
+        <v>564</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4556,17 +4576,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>13250140</t>
+          <t>1983254989</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13250140</t>
+          <t>https://m.place.naver.com/place/1983254989</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4660,7 +4680,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4672,34 +4692,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>메리놀병원</t>
+          <t>부산성모병원</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>maryknollhos@naver.com</t>
+          <t>bsmhospital@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>051-465-8801</t>
+          <t>051-933-7777</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>부산광역시 중구 중구로 121 메리놀병원</t>
+          <t>부산광역시 남구 용호로232번길 25-14 부산성모병원</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>http://www.maryknoll.co.kr/</t>
+          <t>https://bsm.or.kr</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4709,7 +4729,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4720,22 +4740,22 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>548</v>
+        <v>420</v>
       </c>
       <c r="Q46" t="n">
-        <v>323</v>
+        <v>366</v>
       </c>
       <c r="R46" t="n">
-        <v>871</v>
+        <v>786</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4744,17 +4764,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>12070459</t>
+          <t>11814866</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12070459</t>
+          <t>https://m.place.naver.com/place/11814866</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4766,34 +4786,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>부산성모병원</t>
+          <t>메리놀병원</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>bsmhospital@naver.com</t>
+          <t>wwwjpgokr@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>051-933-7777</t>
+          <t>051-465-8801</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>부산광역시 남구 용호로232번길 25-14 부산성모병원</t>
+          <t>부산광역시 중구 중구로 121 메리놀병원</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://bsm.or.kr</t>
+          <t>http://www.maryknoll.co.kr/</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4803,7 +4823,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4814,22 +4834,22 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>418</v>
+        <v>553</v>
       </c>
       <c r="Q47" t="n">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="R47" t="n">
-        <v>770</v>
+        <v>904</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4838,17 +4858,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>11814866</t>
+          <t>12070459</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11814866</t>
+          <t>https://m.place.naver.com/place/12070459</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4860,29 +4880,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>신세계한방병원</t>
+          <t>예성한방병원 부산</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ssghani@naver.com</t>
+          <t>topten0012@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1429-0042</t>
+          <t>051-461-0001</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>부산광역시 서구 구덕로 95 3층, 4층, 6층 신세계한방병원</t>
+          <t>부산광역시 중구 중앙대로 26 6층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://ssgmedi.co.kr/</t>
+          <t>http://ys-hani.co.kr/</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4913,17 +4933,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>198</v>
+        <v>575</v>
       </c>
       <c r="Q48" t="n">
-        <v>562</v>
+        <v>992</v>
       </c>
       <c r="R48" t="n">
-        <v>760</v>
+        <v>1567</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4932,17 +4952,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1648001829</t>
+          <t>2073338996</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1648001829</t>
+          <t>https://m.place.naver.com/place/2073338996</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5014,10 +5034,10 @@
         <v>554</v>
       </c>
       <c r="Q49" t="n">
-        <v>2156</v>
+        <v>2191</v>
       </c>
       <c r="R49" t="n">
-        <v>2710</v>
+        <v>2745</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5036,46 +5056,46 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>한방병원</t>
+          <t>한의원</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>예성한방병원 부산</t>
+          <t>제원한의원</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>amd6629@naver.com</t>
+          <t>wisestream@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>051-461-0001</t>
+          <t>051-415-3560</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>부산광역시 중구 중앙대로 26 6층</t>
+          <t>부산광역시 영도구 태종로 144</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>http://ys-hani.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5085,7 +5105,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5096,7 +5116,7 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5105,13 +5125,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>506</v>
+        <v>80</v>
       </c>
       <c r="Q50" t="n">
-        <v>1062</v>
+        <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>1568</v>
+        <v>81</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5120,17 +5140,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>2073338996</t>
+          <t>13250139</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2073338996</t>
+          <t>https://m.place.naver.com/place/13250139</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5142,39 +5162,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>광덕안정한의원 부산남포동점</t>
+          <t>큰사랑한의원</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>gdaj05111@naver.com</t>
+          <t>mk661117@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>051-243-1075</t>
+          <t>051-417-6337</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>부산광역시 중구 보수대로 14 2층</t>
+          <t>부산광역시 영도구 태종로 93</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://gdaj.net/go/?k=po&amp;slug=bsjunggu&amp;utm_source=NAVER&amp;utm_medium=place</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5195,17 +5215,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="Q51" t="n">
-        <v>2805</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>3231</v>
+        <v>21</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5214,17 +5234,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1111143695</t>
+          <t>13250182</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1111143695</t>
+          <t>https://m.place.naver.com/place/13250182</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5236,25 +5256,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>부경한의원</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>은혜한의원</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>gracekmd@naver.com</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>051-412-0106</t>
+          <t>051-403-7048</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 청학로 86</t>
+          <t>부산광역시 영도구 절영로 560</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.egraceclinic.co.kr/</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5264,7 +5288,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5289,13 +5313,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5304,17 +5328,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1748023823</t>
+          <t>13250064</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1748023823</t>
+          <t>https://m.place.naver.com/place/13250064</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5326,24 +5350,24 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>부산한의원</t>
+          <t>제영한의원</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>thehimchan2@naver.com</t>
+          <t>dkebsptm357@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1400-8101</t>
+          <t>051-404-1275</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 98 . 305호</t>
+          <t>부산광역시 영도구 동삼로 105</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5383,13 +5407,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>110</v>
+        <v>51</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>110</v>
+        <v>51</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5398,17 +5422,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>11720914</t>
+          <t>13250073</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11720914</t>
+          <t>https://m.place.naver.com/place/13250073</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5420,24 +5444,24 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>영도한의원</t>
+          <t>약손한의원</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>seongbok-clinic@naver.com</t>
+          <t>mts6543@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>051-412-0075</t>
+          <t>051-405-7501</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 109 2층</t>
+          <t>부산광역시 영도구 동삼로 23 2층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5477,13 +5501,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>123</v>
+        <v>29</v>
       </c>
       <c r="Q54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>127</v>
+        <v>29</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5492,17 +5516,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1110280284</t>
+          <t>1565191979</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1110280284</t>
+          <t>https://m.place.naver.com/place/1565191979</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5514,40 +5538,44 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>장생한의원</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>경희은한의원</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>drjjoon@naver.com</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>051-403-1432</t>
+          <t>051-631-1300</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼로 64</t>
+          <t>부산광역시 영도구 남항로 51 2층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://feelhani.com/</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5567,13 +5595,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R55" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5582,17 +5610,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>13250054</t>
+          <t>1651788257</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13250054</t>
+          <t>https://m.place.naver.com/place/1651788257</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5604,20 +5632,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>이정원한의원</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>보민한의원</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>leedongh1111@naver.com</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>051-418-1075</t>
+          <t>051-413-1275</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 381</t>
+          <t>부산광역시 영도구 태종로 137 2층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5657,13 +5689,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>276</v>
+        <v>58</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R56" t="n">
-        <v>276</v>
+        <v>60</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5672,17 +5704,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>13250191</t>
+          <t>33050067</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13250191</t>
+          <t>https://m.place.naver.com/place/33050067</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5694,24 +5726,24 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>아남한의원</t>
+          <t>해민한의원</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>g-bean@naver.com</t>
+          <t>the_75@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>051-418-0048</t>
+          <t>051-412-7513</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 절영로 117-3</t>
+          <t>부산광역시 영도구 대교로 11</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5751,13 +5783,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>56</v>
+        <v>195</v>
       </c>
       <c r="Q57" t="n">
         <v>1</v>
       </c>
       <c r="R57" t="n">
-        <v>57</v>
+        <v>196</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5766,17 +5798,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>13250187</t>
+          <t>1665998757</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13250187</t>
+          <t>https://m.place.naver.com/place/1665998757</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5870,7 +5902,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5882,34 +5914,34 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>제원한의원</t>
+          <t>삼세한의원</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>wisestream@naver.com</t>
+          <t>samseluv@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>051-415-3560</t>
+          <t>051-418-7777</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 144</t>
+          <t>부산광역시 영도구 절영로 30 7층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.samse.co.kr/clinic/</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5919,7 +5951,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5935,17 +5967,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>80</v>
+        <v>3185</v>
       </c>
       <c r="Q59" t="n">
-        <v>1</v>
+        <v>168</v>
       </c>
       <c r="R59" t="n">
-        <v>81</v>
+        <v>3353</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5954,17 +5986,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>13250139</t>
+          <t>11523184</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13250139</t>
+          <t>https://m.place.naver.com/place/11523184</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5976,34 +6008,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>삼세한의원</t>
+          <t>태종대한의원</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>samseluv@naver.com</t>
+          <t>dldudvydjl@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>051-418-7777</t>
+          <t>051-403-7866</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 절영로 30 7층</t>
+          <t>부산광역시 영도구 동삼로 50</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://www.samse.co.kr/clinic/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6013,7 +6045,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6029,17 +6061,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3099</v>
+        <v>14</v>
       </c>
       <c r="Q60" t="n">
-        <v>163</v>
+        <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>3262</v>
+        <v>15</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6048,17 +6080,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>11523184</t>
+          <t>13250066</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11523184</t>
+          <t>https://m.place.naver.com/place/13250066</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6070,20 +6102,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>본디올청학한의원</t>
+          <t>경래한의원</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>brandbondam@naver.com</t>
+          <t>g-bean@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>051-416-2525</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 325</t>
+          <t>부산광역시 영도구 대교로 6</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6123,13 +6159,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6138,17 +6174,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>12036959</t>
+          <t>13250119</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12036959</t>
+          <t>https://m.place.naver.com/place/13250119</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6160,20 +6196,24 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>김용호한의원</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>부경한의원</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>chamkmc_new1@naver.com</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>051-414-8480</t>
+          <t>051-412-0106</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 341-15 1층</t>
+          <t>부산광역시 영도구 청학로 86</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6213,13 +6253,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6228,17 +6268,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1155309001</t>
+          <t>1748023823</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1155309001</t>
+          <t>https://m.place.naver.com/place/1748023823</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6250,39 +6290,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>원회춘한의원</t>
+          <t>광덕안정한의원 부산남포동점</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>g-bean@naver.com</t>
+          <t>gdaj05111@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>051-416-4687</t>
+          <t>051-243-1075</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 125-2</t>
+          <t>부산광역시 중구 보수대로 14 2층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://gdaj.net/go/?k=po&amp;slug=bsjunggu&amp;utm_source=NAVER&amp;utm_medium=place</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6303,17 +6343,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>10</v>
+        <v>426</v>
       </c>
       <c r="Q63" t="n">
-        <v>1</v>
+        <v>2824</v>
       </c>
       <c r="R63" t="n">
-        <v>11</v>
+        <v>3250</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6322,17 +6362,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>19525839</t>
+          <t>1111143695</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19525839</t>
+          <t>https://m.place.naver.com/place/1111143695</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6344,29 +6384,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>성복한의원</t>
+          <t>본디올청학한의원</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>seongbok-clinic@naver.com</t>
+          <t>brandbondam@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>051-413-1741</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 절영로 98</t>
+          <t>부산광역시 영도구 태종로 325</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/seongbok-clinic</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6376,12 +6412,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6401,13 +6437,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="Q64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6416,17 +6452,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>13250116</t>
+          <t>12036959</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13250116</t>
+          <t>https://m.place.naver.com/place/12036959</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6438,20 +6474,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>보민한의원</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>더조은한의원</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>kkslmjlove@naver.com</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>051-413-1275</t>
+          <t>051-418-7575</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 137 2층</t>
+          <t>부산광역시 영도구 태종로 139 6층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6491,13 +6531,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="Q65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R65" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6506,17 +6546,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>33050067</t>
+          <t>1604234168</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33050067</t>
+          <t>https://m.place.naver.com/place/1604234168</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6528,24 +6568,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>태종대한의원</t>
+          <t>영도한의원</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>dldudvydjl@naver.com</t>
+          <t>seongbok-clinic@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>051-403-7866</t>
+          <t>051-412-0075</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼로 50</t>
+          <t>부산광역시 영도구 태종로 109 2층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6585,13 +6625,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>14</v>
+        <v>123</v>
       </c>
       <c r="Q66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R66" t="n">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6600,17 +6640,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>13250066</t>
+          <t>1110280284</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13250066</t>
+          <t>https://m.place.naver.com/place/1110280284</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6622,24 +6662,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>해민한의원</t>
+          <t>김용호한의원</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>the_75@naver.com</t>
+          <t>brandbondam@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>051-412-7513</t>
+          <t>051-414-8480</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 대교로 11</t>
+          <t>부산광역시 영도구 태종로 341-15 1층</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6679,14 +6719,14 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>195</v>
+        <v>1</v>
       </c>
       <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
         <v>1</v>
       </c>
-      <c r="R67" t="n">
-        <v>196</v>
-      </c>
       <c r="S67" t="inlineStr">
         <is>
           <t>X</t>
@@ -6694,17 +6734,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1665998757</t>
+          <t>1155309001</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1665998757</t>
+          <t>https://m.place.naver.com/place/1155309001</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6716,44 +6756,44 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>경희은한의원</t>
+          <t>원회춘한의원</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>drjjoon@naver.com</t>
+          <t>g-bean@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>051-631-1300</t>
+          <t>051-416-4687</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 남항로 51 2층</t>
+          <t>부산광역시 영도구 태종로 125-2</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>http://feelhani.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6773,13 +6813,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q68" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="R68" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6788,17 +6828,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1651788257</t>
+          <t>19525839</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1651788257</t>
+          <t>https://m.place.naver.com/place/19525839</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6810,24 +6850,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>제영한의원</t>
+          <t>온마음한의원</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>broadcast576@naver.com</t>
+          <t>goodverte@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>051-404-1275</t>
+          <t>051-417-7588</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼로 105</t>
+          <t>부산광역시 영도구 영선대로 109 고려빌딩 1층.3층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6867,13 +6907,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>51</v>
+        <v>131</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R69" t="n">
-        <v>51</v>
+        <v>135</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6882,17 +6922,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>13250073</t>
+          <t>32015124</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13250073</t>
+          <t>https://m.place.naver.com/place/32015124</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6904,20 +6944,24 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>큰사랑한의원</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>홍상철한의원</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>g-bean@naver.com</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>051-417-6337</t>
+          <t>051-418-1575</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 93</t>
+          <t>부산광역시 영도구 태종로113번길 33</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6957,13 +7001,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6972,17 +7016,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>13250182</t>
+          <t>19525873</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13250182</t>
+          <t>https://m.place.naver.com/place/19525873</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6994,29 +7038,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>경래한의원</t>
+          <t>성복한의원</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>g-bean@naver.com</t>
+          <t>seongbok-clinic@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>051-416-2525</t>
+          <t>051-413-1741</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 대교로 6</t>
+          <t>부산광역시 영도구 절영로 98</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/seongbok-clinic</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7026,12 +7070,12 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7051,13 +7095,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="Q71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R71" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7066,17 +7110,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>13250119</t>
+          <t>13250116</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13250119</t>
+          <t>https://m.place.naver.com/place/13250116</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7132,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>홍상철한의원</t>
+          <t>아남한의원</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -7099,13 +7143,13 @@
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>051-418-1575</t>
+          <t>051-418-0048</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로113번길 33</t>
+          <t>부산광역시 영도구 절영로 117-3</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7145,13 +7189,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="Q72" t="n">
         <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7160,17 +7204,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>19525873</t>
+          <t>13250187</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19525873</t>
+          <t>https://m.place.naver.com/place/13250187</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7182,24 +7226,24 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>온마음한의원</t>
+          <t>부산한의원</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>goodverte@naver.com</t>
+          <t>balancehani@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>051-417-7588</t>
+          <t>0507-1400-8101</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 영선대로 109 고려빌딩 1층.3층</t>
+          <t>부산광역시 영도구 태종로 98 . 305호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7239,13 +7283,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="Q73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7254,17 +7298,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>32015124</t>
+          <t>11720914</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32015124</t>
+          <t>https://m.place.naver.com/place/11720914</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7276,20 +7320,24 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>더조은한의원</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>이정원한의원</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>hjkim1069@naver.com</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>051-418-7575</t>
+          <t>051-418-1075</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 139 6층</t>
+          <t>부산광역시 영도구 태종로 381</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7329,13 +7377,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>10</v>
+        <v>276</v>
       </c>
       <c r="Q74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>11</v>
+        <v>276</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7344,17 +7392,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1604234168</t>
+          <t>13250191</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1604234168</t>
+          <t>https://m.place.naver.com/place/13250191</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7366,34 +7414,34 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>약손한의원</t>
+          <t>자연안에한의원 중구점</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>arasi100@naver.com</t>
+          <t>jjhye_ppiness@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>051-405-7501</t>
+          <t>051-242-1075</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼로 23 2층</t>
+          <t>부산광역시 중구 구덕로 80 2층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.naturemed.co.kr/</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7403,7 +7451,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7414,22 +7462,22 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>29</v>
+        <v>494</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="R75" t="n">
-        <v>29</v>
+        <v>1474</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7438,17 +7486,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1565191979</t>
+          <t>1908902363</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1565191979</t>
+          <t>https://m.place.naver.com/place/1908902363</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7460,29 +7508,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>은혜한의원</t>
+          <t>장생한의원</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>gracekmd@naver.com</t>
+          <t>zema77@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>051-403-7048</t>
+          <t>051-403-1432</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 절영로 560</t>
+          <t>부산광역시 영도구 동삼로 64</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>http://www.egraceclinic.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7492,7 +7540,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7517,13 +7565,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="Q76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7532,17 +7580,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>13250064</t>
+          <t>13250054</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13250064</t>
+          <t>https://m.place.naver.com/place/13250054</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
